--- a/exports/JSWSTEEL_full_report.xlsx
+++ b/exports/JSWSTEEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.03</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>666.85</v>
+        <v>630.55</v>
       </c>
       <c r="I2" t="n">
         <v>658.0238043333374</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.03</v>
+        <v>-6.42</v>
       </c>
       <c r="L2" t="n">
-        <v>4.53</v>
+        <v>6.92</v>
       </c>
       <c r="M2" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="N2" t="n">
-        <v>3.51</v>
+        <v>7.01</v>
       </c>
       <c r="O2" t="n">
         <v>0.11</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>10.03</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44601.55208333334</v>
+        <v>44602.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>662.65</v>
+        <v>674</v>
       </c>
       <c r="I3" t="n">
         <v>671.1059286999713</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.09</v>
+        <v>-6.89</v>
       </c>
       <c r="L3" t="n">
-        <v>5.84</v>
+        <v>7.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>5.99</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>668.45</v>
+        <v>632.8</v>
       </c>
       <c r="I4" t="n">
         <v>638.3547099212626</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.82</v>
+        <v>-6.11</v>
       </c>
       <c r="L4" t="n">
-        <v>2.13</v>
+        <v>7.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.45</v>
+        <v>1.82</v>
       </c>
       <c r="N4" t="n">
-        <v>0.53</v>
+        <v>6.06</v>
       </c>
       <c r="O4" t="n">
         <v>1.41</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44617.55208333334</v>
+        <v>44620.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>598.4</v>
+        <v>625.45</v>
       </c>
       <c r="I5" t="n">
         <v>622.5834413472066</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>5.44</v>
+        <v>1.16</v>
       </c>
       <c r="L5" t="n">
         <v>4.9</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.6</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.38541666666</v>
+        <v>44673.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>729.15</v>
+        <v>724.5</v>
       </c>
       <c r="I6" t="n">
         <v>729.0863693522297</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>16.58</v>
+        <v>15.84</v>
       </c>
       <c r="L6" t="n">
         <v>5.61</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.57</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44755.38541666666</v>
+        <v>44755.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>582.8</v>
+        <v>587.6</v>
       </c>
       <c r="I7" t="n">
         <v>585.4495581724134</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>81.83333333333333</v>
+        <v>82</v>
       </c>
       <c r="K7" t="n">
-        <v>19.56</v>
+        <v>18.9</v>
       </c>
       <c r="L7" t="n">
         <v>2.14</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.99</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>663.1</v>
+        <v>647.2</v>
       </c>
       <c r="I8" t="n">
         <v>649.5226667143436</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>37</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K8" t="n">
-        <v>12.85</v>
+        <v>10.14</v>
       </c>
       <c r="L8" t="n">
         <v>3.11</v>
@@ -897,7 +992,7 @@
         <v>1.62</v>
       </c>
       <c r="N8" t="n">
-        <v>1.69</v>
+        <v>2.97</v>
       </c>
       <c r="O8" t="n">
         <v>2.71</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>5.24</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44806.55208333334</v>
+        <v>44809.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>661</v>
+        <v>678.5</v>
       </c>
       <c r="I9" t="n">
         <v>671.3677433687191</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.13</v>
+        <v>-4.84</v>
       </c>
       <c r="L9" t="n">
-        <v>3.61</v>
+        <v>5.12</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>3.18</v>
       </c>
       <c r="O9" t="n">
         <v>-2.97</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>6.06</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>668.45</v>
+        <v>653.35</v>
       </c>
       <c r="I10" t="n">
         <v>665.9694040920821</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.48</v>
+        <v>-3.71</v>
       </c>
       <c r="L10" t="n">
-        <v>2.43</v>
+        <v>5.97</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="N10" t="n">
-        <v>1.63</v>
+        <v>3.07</v>
       </c>
       <c r="O10" t="n">
         <v>3.18</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>5.11</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>644.7</v>
+        <v>671.4</v>
       </c>
       <c r="I11" t="n">
         <v>657.1108055155978</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>1.32</v>
+        <v>-2.76</v>
       </c>
       <c r="L11" t="n">
-        <v>1.07</v>
+        <v>2.82</v>
       </c>
       <c r="M11" t="n">
         <v>1.65</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
         <v>-3.07</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>7.49</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44848.55208333334</v>
+        <v>44851.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>639</v>
+        <v>630.3</v>
       </c>
       <c r="I12" t="n">
         <v>634.962300945598</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.83</v>
+        <v>-6.12</v>
       </c>
       <c r="L12" t="n">
-        <v>4.94</v>
+        <v>7.06</v>
       </c>
       <c r="M12" t="n">
         <v>1.7</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>5.87</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44859.55208333334</v>
+        <v>44861.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>644.3</v>
+        <v>674.8</v>
       </c>
       <c r="I13" t="n">
         <v>651.5499255137956</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.22</v>
+        <v>-7.06</v>
       </c>
       <c r="L13" t="n">
-        <v>3.27</v>
+        <v>7.73</v>
       </c>
       <c r="M13" t="n">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>5.85</v>
       </c>
       <c r="O13" t="n">
         <v>-1.1</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.74</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>736.65</v>
+        <v>730.25</v>
       </c>
       <c r="I14" t="n">
         <v>731.6069613192245</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K14" t="n">
-        <v>9.17</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>3.68</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>3.93</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44921.55208333334</v>
+        <v>44922.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>730.3</v>
+        <v>760.15</v>
       </c>
       <c r="I15" t="n">
         <v>758.3694764561867</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.01</v>
+        <v>-4.09</v>
       </c>
       <c r="L15" t="n">
-        <v>0.97</v>
+        <v>4.21</v>
       </c>
       <c r="M15" t="n">
-        <v>0.16</v>
+        <v>0.77</v>
       </c>
       <c r="N15" t="n">
-        <v>0.54</v>
+        <v>4.57</v>
       </c>
       <c r="O15" t="n">
         <v>-1.39</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.3</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44929.55208333334</v>
+        <v>44930.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>767.5</v>
+        <v>743.5</v>
       </c>
       <c r="I16" t="n">
         <v>745.223424071505</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.97</v>
+        <v>-2.19</v>
       </c>
       <c r="L16" t="n">
         <v>3.38</v>
@@ -1353,7 +1544,7 @@
         <v>0.79</v>
       </c>
       <c r="N16" t="n">
-        <v>1.11</v>
+        <v>4.11</v>
       </c>
       <c r="O16" t="n">
         <v>4.57</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>6.39</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44944.55208333334</v>
+        <v>44945.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>767.55</v>
+        <v>769</v>
       </c>
       <c r="I17" t="n">
         <v>767.6544700767924</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.23</v>
+        <v>-3.43</v>
       </c>
       <c r="L17" t="n">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="M17" t="n">
         <v>1.2</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>4.84</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44949.55208333334</v>
+        <v>44950.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>735</v>
+        <v>728.55</v>
       </c>
       <c r="I18" t="n">
         <v>731.7768904975919</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.42</v>
+        <v>-5.26</v>
       </c>
       <c r="L18" t="n">
-        <v>5.59</v>
+        <v>5.83</v>
       </c>
       <c r="M18" t="n">
         <v>0.73</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.38</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>676.6</v>
+        <v>689.8</v>
       </c>
       <c r="I19" t="n">
         <v>686.8337701790782</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>64.16666666666667</v>
+        <v>66</v>
       </c>
       <c r="K19" t="n">
-        <v>7.13</v>
+        <v>5.32</v>
       </c>
       <c r="L19" t="n">
         <v>1.39</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>5.38</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45057.55208333334</v>
+        <v>45058.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>710.1</v>
+        <v>704</v>
       </c>
       <c r="I20" t="n">
         <v>709.034470320424</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K20" t="n">
-        <v>2.94</v>
+        <v>2.06</v>
       </c>
       <c r="L20" t="n">
         <v>2.14</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="N20" t="n">
         <v>1.92</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>3.65</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45084.38541666666</v>
+        <v>45084.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>716.85</v>
+        <v>731.5</v>
       </c>
       <c r="I21" t="n">
         <v>718.5310819065929</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.83</v>
+        <v>-3.91</v>
       </c>
       <c r="L21" t="n">
-        <v>2.48</v>
+        <v>4.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.95</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>747.65</v>
+        <v>745</v>
       </c>
       <c r="I22" t="n">
         <v>745.8133467764807</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K22" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="L22" t="n">
         <v>2.03</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>4.71</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45104.55208333334</v>
+        <v>45105.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>762.25</v>
+        <v>784</v>
       </c>
       <c r="I23" t="n">
         <v>777.1626242153659</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.32</v>
+        <v>-5.23</v>
       </c>
       <c r="L23" t="n">
-        <v>2.68</v>
+        <v>5.91</v>
       </c>
       <c r="M23" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
         <v>-1.01</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.99</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45154.55208333334</v>
+        <v>45155.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>794.45</v>
+        <v>785.85</v>
       </c>
       <c r="I24" t="n">
         <v>794.0751704236277</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K24" t="n">
-        <v>1.33</v>
+        <v>0.24</v>
       </c>
       <c r="L24" t="n">
         <v>2.81</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>5.12</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45170.38541666666</v>
+        <v>45170.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>794.85</v>
+        <v>807</v>
       </c>
       <c r="I25" t="n">
         <v>801.943530033276</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.15</v>
+        <v>-2.69</v>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="M25" t="n">
         <v>0.9</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>4.84</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45187.55208333334</v>
+        <v>45189.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>808.9</v>
+        <v>792.5</v>
       </c>
       <c r="I26" t="n">
         <v>793.6364509755197</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>0.24</v>
+        <v>-1.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="M26" t="n">
         <v>0.12</v>
       </c>
       <c r="N26" t="n">
-        <v>0.82</v>
+        <v>2.71</v>
       </c>
       <c r="O26" t="n">
         <v>3.42</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>5.27</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45210.55208333334</v>
+        <v>45211.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>776.1</v>
+        <v>785</v>
       </c>
       <c r="I27" t="n">
         <v>782.6683864778172</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K27" t="n">
-        <v>2.07</v>
+        <v>0.95</v>
       </c>
       <c r="L27" t="n">
         <v>2.31</v>
       </c>
       <c r="M27" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>2.08</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>3.67</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>779</v>
+        <v>764.1</v>
       </c>
       <c r="I28" t="n">
         <v>765.8326836600513</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.76</v>
+        <v>-2.66</v>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>2.79</v>
       </c>
       <c r="M28" t="n">
         <v>0.83</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45239.55208333334</v>
+        <v>45240.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>750.45</v>
+        <v>757.15</v>
       </c>
       <c r="I29" t="n">
         <v>756.3047538156608</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K29" t="n">
-        <v>1.79</v>
+        <v>0.91</v>
       </c>
       <c r="L29" t="n">
         <v>2.05</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>4.45</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>869.25</v>
+        <v>841.2</v>
       </c>
       <c r="I30" t="n">
         <v>843.2664246572767</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K30" t="n">
-        <v>14.81</v>
+        <v>11.1</v>
       </c>
       <c r="L30" t="n">
         <v>1.6</v>
@@ -2151,7 +2510,7 @@
         <v>2.54</v>
       </c>
       <c r="N30" t="n">
-        <v>1.87</v>
+        <v>3.66</v>
       </c>
       <c r="O30" t="n">
         <v>0.36</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>6.74</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45328.55208333334</v>
+        <v>45329.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>820</v>
+        <v>839.55</v>
       </c>
       <c r="I31" t="n">
         <v>830.7954897037744</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K31" t="n">
-        <v>2.52</v>
+        <v>0.2</v>
       </c>
       <c r="L31" t="n">
         <v>3.42</v>
       </c>
       <c r="M31" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="N31" t="n">
         <v>2.62</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>6.06</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>804.55</v>
+        <v>789.3</v>
       </c>
       <c r="I32" t="n">
         <v>795.8748832152863</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.17</v>
+        <v>-5.99</v>
       </c>
       <c r="L32" t="n">
-        <v>5.9</v>
+        <v>6.09</v>
       </c>
       <c r="M32" t="n">
         <v>1.85</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>6.73</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45372.55208333334</v>
+        <v>45373.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>812</v>
+        <v>829.6</v>
       </c>
       <c r="I33" t="n">
         <v>827.8319806720672</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.88</v>
+        <v>-5.11</v>
       </c>
       <c r="L33" t="n">
-        <v>3.82</v>
+        <v>5.26</v>
       </c>
       <c r="M33" t="n">
         <v>1.37</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.09</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>863</v>
+        <v>843.1</v>
       </c>
       <c r="I34" t="n">
         <v>852.7527630541354</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K34" t="n">
-        <v>4.03</v>
+        <v>1.63</v>
       </c>
       <c r="L34" t="n">
         <v>2.75</v>
@@ -2379,7 +2786,7 @@
         <v>0.72</v>
       </c>
       <c r="N34" t="n">
-        <v>2.73</v>
+        <v>3.36</v>
       </c>
       <c r="O34" t="n">
         <v>0.99</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>7.42</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45428.55208333334</v>
+        <v>45429.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>884</v>
+        <v>910.3</v>
       </c>
       <c r="I35" t="n">
         <v>887.8883252704579</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.85</v>
+        <v>-7.97</v>
       </c>
       <c r="L35" t="n">
-        <v>5.38</v>
+        <v>8.52</v>
       </c>
       <c r="M35" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="N35" t="n">
         <v>2.28</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.42</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>914.9</v>
+        <v>854.4</v>
       </c>
       <c r="I36" t="n">
         <v>869.5406188377725</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K36" t="n">
-        <v>0.51</v>
+        <v>-6.14</v>
       </c>
       <c r="L36" t="n">
-        <v>4.07</v>
+        <v>9.5</v>
       </c>
       <c r="M36" t="n">
         <v>1.54</v>
       </c>
       <c r="N36" t="n">
-        <v>1.56</v>
+        <v>7.09</v>
       </c>
       <c r="O36" t="n">
         <v>2.26</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>10.21</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45454.55208333334</v>
+        <v>45455.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>910.05</v>
+        <v>921.55</v>
       </c>
       <c r="I37" t="n">
         <v>921.1609792669319</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.51</v>
+        <v>-7.86</v>
       </c>
       <c r="L37" t="n">
-        <v>7.68</v>
+        <v>8.18</v>
       </c>
       <c r="M37" t="n">
         <v>1.03</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.77</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45483.55208333334</v>
+        <v>45484.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>924</v>
+        <v>918.1</v>
       </c>
       <c r="I38" t="n">
         <v>919.522142379922</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K38" t="n">
-        <v>0.27</v>
+        <v>-0.37</v>
       </c>
       <c r="L38" t="n">
         <v>1.95</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>4.38</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45503.55208333334</v>
+        <v>45504.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>903</v>
+        <v>923.85</v>
       </c>
       <c r="I39" t="n">
         <v>914.4364912125823</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>1.64</v>
+        <v>-0.63</v>
       </c>
       <c r="L39" t="n">
         <v>2.31</v>
@@ -2664,7 +3131,7 @@
         <v>1.21</v>
       </c>
       <c r="N39" t="n">
-        <v>2.86</v>
+        <v>3.32</v>
       </c>
       <c r="O39" t="n">
         <v>0.11</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>5.79</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>898</v>
+        <v>860.5</v>
       </c>
       <c r="I40" t="n">
         <v>893.565550010472</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.8</v>
+        <v>-6.86</v>
       </c>
       <c r="L40" t="n">
-        <v>3.01</v>
+        <v>7.54</v>
       </c>
       <c r="M40" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="N40" t="n">
-        <v>3.53</v>
+        <v>4.12</v>
       </c>
       <c r="O40" t="n">
         <v>3.32</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.68</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45524.55208333334</v>
+        <v>45525.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>916</v>
+        <v>923.95</v>
       </c>
       <c r="I41" t="n">
         <v>919.8165068743165</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.45</v>
+        <v>-7.37</v>
       </c>
       <c r="L41" t="n">
         <v>7.79</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.68</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45580.55208333334</v>
+        <v>45581.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1001.8</v>
+        <v>985.4</v>
       </c>
       <c r="I42" t="n">
         <v>991.9520385396155</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K42" t="n">
-        <v>8.43</v>
+        <v>6.65</v>
       </c>
       <c r="L42" t="n">
         <v>1.72</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.1</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45601.38541666666</v>
+        <v>45601.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>985.8</v>
+        <v>1001</v>
       </c>
       <c r="I43" t="n">
         <v>989.0330795250925</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.04</v>
+        <v>-1.58</v>
       </c>
       <c r="L43" t="n">
         <v>1.99</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>6.47</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>955.95</v>
+        <v>934.05</v>
       </c>
       <c r="I44" t="n">
         <v>947.4292602265897</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.5</v>
+        <v>-6.69</v>
       </c>
       <c r="L44" t="n">
-        <v>4.73</v>
+        <v>6.98</v>
       </c>
       <c r="M44" t="n">
         <v>0.7</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>7.36</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45628.38541666666</v>
+        <v>45628.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>981.75</v>
+        <v>990.4</v>
       </c>
       <c r="I45" t="n">
         <v>990.0699704761307</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.11</v>
+        <v>-6.03</v>
       </c>
       <c r="L45" t="n">
-        <v>5.22</v>
+        <v>6.16</v>
       </c>
       <c r="M45" t="n">
         <v>0.19</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>4.9</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45643.38541666666</v>
+        <v>45643.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>972.8</v>
+        <v>961</v>
       </c>
       <c r="I46" t="n">
         <v>972.3810634257898</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.78</v>
+        <v>-2.97</v>
       </c>
       <c r="L46" t="n">
-        <v>1.8</v>
+        <v>2.97</v>
       </c>
       <c r="M46" t="n">
         <v>0.74</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.36</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45677.55208333334</v>
+        <v>45678.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="I47" t="n">
         <v>924.6936651935411</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K47" t="n">
-        <v>4.06</v>
+        <v>3.54</v>
       </c>
       <c r="L47" t="n">
         <v>1.27</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.18</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1042.1</v>
+        <v>1009.9</v>
       </c>
       <c r="I48" t="n">
         <v>1022.916099815124</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>72.16666666666667</v>
+        <v>73</v>
       </c>
       <c r="K48" t="n">
-        <v>12.42</v>
+        <v>8.94</v>
       </c>
       <c r="L48" t="n">
         <v>2.79</v>
@@ -3177,7 +3752,7 @@
         <v>3.31</v>
       </c>
       <c r="N48" t="n">
-        <v>2.16</v>
+        <v>3.24</v>
       </c>
       <c r="O48" t="n">
         <v>0.23</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.62</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>992.7</v>
+        <v>1005.2</v>
       </c>
       <c r="I49" t="n">
         <v>994.8906440476694</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K49" t="n">
-        <v>1.7</v>
+        <v>0.47</v>
       </c>
       <c r="L49" t="n">
         <v>2.88</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>6.53</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1025.1</v>
+        <v>966.3</v>
       </c>
       <c r="I50" t="n">
         <v>993.2152367620024</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K50" t="n">
-        <v>1.98</v>
+        <v>-3.87</v>
       </c>
       <c r="L50" t="n">
-        <v>1.8</v>
+        <v>5.66</v>
       </c>
       <c r="M50" t="n">
         <v>1.4</v>
       </c>
       <c r="N50" t="n">
-        <v>2.1</v>
+        <v>5.38</v>
       </c>
       <c r="O50" t="n">
         <v>1.77</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.64</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>1000.9</v>
+        <v>1003.9</v>
       </c>
       <c r="I51" t="n">
         <v>1002.336186101856</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.58</v>
+        <v>-3.89</v>
       </c>
       <c r="L51" t="n">
         <v>7.32</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.72</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45811.38541666666</v>
+        <v>45811.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>974.6</v>
+        <v>974</v>
       </c>
       <c r="I52" t="n">
         <v>974.1310813384445</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>21.83333333333333</v>
+        <v>22</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.92</v>
+        <v>-2.98</v>
       </c>
       <c r="L52" t="n">
         <v>3.45</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,25 +4076,25 @@
         <v>4.7</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>996.5</v>
+        <v>1015.7</v>
       </c>
       <c r="I53" t="n">
         <v>1013.142265584065</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.31</v>
+        <v>-4.28</v>
       </c>
       <c r="L53" t="n">
         <v>5.13</v>
       </c>
       <c r="M53" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="N53" t="n">
         <v>3.36</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.85</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1052.7</v>
+        <v>1041.8</v>
       </c>
       <c r="I54" t="n">
         <v>1042.371221764807</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>65</v>
       </c>
       <c r="K54" t="n">
-        <v>3.64</v>
+        <v>2.57</v>
       </c>
       <c r="L54" t="n">
         <v>1.42</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.14</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45902.55208333334</v>
+        <v>45903.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1043.6</v>
+        <v>1072.9</v>
       </c>
       <c r="I55" t="n">
         <v>1064.133918671891</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.17</v>
+        <v>-2.99</v>
       </c>
       <c r="L55" t="n">
-        <v>1.28</v>
+        <v>3.66</v>
       </c>
       <c r="M55" t="n">
         <v>0.18</v>
       </c>
       <c r="N55" t="n">
-        <v>0.96</v>
+        <v>2.98</v>
       </c>
       <c r="O55" t="n">
         <v>-1.42</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.33</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1168</v>
+        <v>1149.8</v>
       </c>
       <c r="I56" t="n">
         <v>1159.986902993242</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>78.16666666666667</v>
+        <v>79</v>
       </c>
       <c r="K56" t="n">
-        <v>8.859999999999999</v>
+        <v>7.17</v>
       </c>
       <c r="L56" t="n">
         <v>3.07</v>
@@ -3633,7 +4304,7 @@
         <v>0.82</v>
       </c>
       <c r="N56" t="n">
-        <v>1.58</v>
+        <v>2.75</v>
       </c>
       <c r="O56" t="n">
         <v>2.98</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>4.51</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45988.55208333334</v>
+        <v>45989.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1157.9</v>
+        <v>1160.5</v>
       </c>
       <c r="I57" t="n">
         <v>1159.552460481384</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.7</v>
+        <v>-0.93</v>
       </c>
       <c r="L57" t="n">
-        <v>1.49</v>
+        <v>1.98</v>
       </c>
       <c r="M57" t="n">
         <v>0.54</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>4.6</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45999.55208333334</v>
+        <v>46000.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1119.1</v>
+        <v>1111.9</v>
       </c>
       <c r="I58" t="n">
         <v>1115.399469238549</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.57</v>
+        <v>-4.19</v>
       </c>
       <c r="L58" t="n">
-        <v>4.79</v>
+        <v>5.27</v>
       </c>
       <c r="M58" t="n">
         <v>0.44</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.49</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46021.55208333334</v>
+        <v>46022.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1111.5</v>
+        <v>1162.8</v>
       </c>
       <c r="I59" t="n">
         <v>1123.077232253258</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K59" t="n">
-        <v>0.04</v>
+        <v>-4.58</v>
       </c>
       <c r="L59" t="n">
-        <v>1.52</v>
+        <v>5.14</v>
       </c>
       <c r="M59" t="n">
-        <v>0.98</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>2.05</v>
+        <v>4.89</v>
       </c>
       <c r="O59" t="n">
         <v>-1.24</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.61</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1265.7</v>
+        <v>1212.8</v>
       </c>
       <c r="I60" t="n">
         <v>1228.661915589132</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K60" t="n">
-        <v>8.85</v>
+        <v>4.3</v>
       </c>
       <c r="L60" t="n">
         <v>2.6</v>
       </c>
       <c r="M60" t="n">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="N60" t="n">
-        <v>2.57</v>
+        <v>4.55</v>
       </c>
       <c r="O60" t="n">
         <v>4.89</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.85</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46120.55208333334</v>
+        <v>46121.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1192.6</v>
+        <v>1209.4</v>
       </c>
       <c r="I61" t="n">
         <v>1193.053872790603</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K61" t="n">
-        <v>1.67</v>
+        <v>0.28</v>
       </c>
       <c r="L61" t="n">
         <v>3.39</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.07</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>1270.1</v>
+        <v>1258</v>
       </c>
       <c r="I62" t="n">
         <v>1263.136001719853</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>60</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>5.02</v>
+        <v>4.02</v>
       </c>
       <c r="L62" t="n">
         <v>2.02</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.96</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46223.55208333334</v>
+        <v>46224.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1255.5</v>
+        <v>1265.3</v>
       </c>
       <c r="I63" t="n">
         <v>1262.529447030046</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2</v>
+        <v>-0.58</v>
       </c>
       <c r="L63" t="n">
         <v>4.94</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.46</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46246.38541666666</v>
+        <v>46246.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>1274.3</v>
+        <v>1268.6</v>
       </c>
       <c r="I64" t="n">
         <v>1269.203204538436</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>0.71</v>
+        <v>0.26</v>
       </c>
       <c r="L64" t="n">
         <v>2.94</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>3.82</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46255.55208333334</v>
+        <v>46258.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1290.2</v>
+        <v>1311.2</v>
       </c>
       <c r="I65" t="n">
         <v>1306.614767690919</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.7</v>
+        <v>-3.36</v>
       </c>
       <c r="L65" t="n">
-        <v>3.31</v>
+        <v>3.65</v>
       </c>
       <c r="M65" t="n">
         <v>1.45</v>
       </c>
       <c r="N65" t="n">
-        <v>1.18</v>
+        <v>1.98</v>
       </c>
       <c r="O65" t="n">
         <v>-0.67</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>4.26</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46275.55208333334</v>
+        <v>46276.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1295</v>
+        <v>1270</v>
       </c>
       <c r="I66" t="n">
         <v>1293.72896810363</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.24</v>
+        <v>-3.14</v>
       </c>
       <c r="L66" t="n">
-        <v>1.61</v>
+        <v>3.22</v>
       </c>
       <c r="M66" t="n">
-        <v>0.45</v>
+        <v>1.08</v>
       </c>
       <c r="N66" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="O66" t="n">
         <v>1.98</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>4.34</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46287.55208333334</v>
+        <v>46288.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1265.4</v>
+        <v>1291.1</v>
       </c>
       <c r="I67" t="n">
         <v>1288.916257249691</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K67" t="n">
-        <v>0.36</v>
+        <v>-1.66</v>
       </c>
       <c r="L67" t="n">
-        <v>1.34</v>
+        <v>2.68</v>
       </c>
       <c r="M67" t="n">
         <v>1.35</v>
       </c>
       <c r="N67" t="n">
-        <v>1.18</v>
+        <v>2.34</v>
       </c>
       <c r="O67" t="n">
         <v>-2.05</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>4.17</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1261</v>
+        <v>1229.1</v>
       </c>
       <c r="I68" t="n">
         <v>1246.704464276581</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.33</v>
+        <v>-4.8</v>
       </c>
       <c r="L68" t="n">
-        <v>3.45</v>
+        <v>5.48</v>
       </c>
       <c r="M68" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="N68" t="n">
-        <v>1.61</v>
+        <v>2.46</v>
       </c>
       <c r="O68" t="n">
         <v>2.34</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>5.13</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46310.55208333334</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1199.7</v>
+        <v>1224.8</v>
       </c>
       <c r="I69" t="n">
         <v>1224.283962598232</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K69" t="n">
-        <v>2.39</v>
+        <v>0.35</v>
       </c>
       <c r="L69" t="n">
         <v>2.64</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4434,6 +5273,14 @@
       <c r="Q70" t="n">
         <v>16</v>
       </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6536,7 +7383,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.5</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="6">
@@ -6546,7 +7393,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -6556,7 +7403,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
@@ -6566,7 +7413,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6576,7 +7423,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="10">
@@ -6586,7 +7433,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57.3</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -6626,7 +7473,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.16</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="15">
@@ -6636,7 +7483,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.33</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="16">
@@ -6646,7 +7493,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.01</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="17">
@@ -6656,7 +7503,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19.56</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="18">
@@ -6666,7 +7513,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.5</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="19">
@@ -6676,7 +7523,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.19</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="20">
@@ -6686,7 +7533,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="21">
@@ -6696,7 +7543,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.79</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="22">
@@ -6706,7 +7553,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -6726,7 +7573,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="25">
@@ -6736,7 +7583,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -6746,7 +7593,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="27">
@@ -6756,7 +7603,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.87</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="28">
@@ -6766,7 +7613,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
